--- a/public/plantilla-adicionales.xlsx
+++ b/public/plantilla-adicionales.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,11 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -287,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -307,46 +312,46 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -394,17 +399,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -417,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,13 +437,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,10 +473,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +494,48 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1011,11 +1057,11 @@
       </c>
       <c r="B10" s="76" t="n"/>
       <c r="C10" s="77" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="76" t="n"/>
-      <c r="F10" s="76" t="n"/>
-      <c r="G10" s="76" t="n"/>
-      <c r="H10" s="77" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="83" t="n"/>
+      <c r="F10" s="83" t="n"/>
+      <c r="G10" s="83" t="n"/>
+      <c r="H10" s="84" t="n"/>
       <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1023,11 +1069,11 @@
       </c>
       <c r="J10" s="76" t="n"/>
       <c r="K10" s="77" t="n"/>
-      <c r="L10" s="23" t="n"/>
-      <c r="M10" s="76" t="n"/>
-      <c r="N10" s="76" t="n"/>
-      <c r="O10" s="76" t="n"/>
-      <c r="P10" s="77" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="83" t="n"/>
+      <c r="N10" s="83" t="n"/>
+      <c r="O10" s="83" t="n"/>
+      <c r="P10" s="84" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="33">
       <c r="A11" s="21" t="inlineStr">
@@ -1037,11 +1083,11 @@
       </c>
       <c r="B11" s="76" t="n"/>
       <c r="C11" s="77" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="76" t="n"/>
-      <c r="F11" s="76" t="n"/>
-      <c r="G11" s="76" t="n"/>
-      <c r="H11" s="77" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="83" t="n"/>
+      <c r="F11" s="83" t="n"/>
+      <c r="G11" s="83" t="n"/>
+      <c r="H11" s="84" t="n"/>
       <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1049,11 +1095,11 @@
       </c>
       <c r="J11" s="76" t="n"/>
       <c r="K11" s="77" t="n"/>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="76" t="n"/>
-      <c r="N11" s="76" t="n"/>
-      <c r="O11" s="76" t="n"/>
-      <c r="P11" s="77" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="83" t="n"/>
+      <c r="O11" s="83" t="n"/>
+      <c r="P11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="33">
       <c r="A12" s="21" t="inlineStr">
@@ -1063,11 +1109,11 @@
       </c>
       <c r="B12" s="76" t="n"/>
       <c r="C12" s="77" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="76" t="n"/>
-      <c r="F12" s="76" t="n"/>
-      <c r="G12" s="76" t="n"/>
-      <c r="H12" s="77" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="83" t="n"/>
+      <c r="F12" s="83" t="n"/>
+      <c r="G12" s="83" t="n"/>
+      <c r="H12" s="84" t="n"/>
       <c r="I12" s="21" t="inlineStr">
         <is>
           <t>Plazo del contrato (días)</t>
@@ -1075,11 +1121,11 @@
       </c>
       <c r="J12" s="76" t="n"/>
       <c r="K12" s="77" t="n"/>
-      <c r="L12" s="23" t="n"/>
-      <c r="M12" s="76" t="n"/>
-      <c r="N12" s="76" t="n"/>
-      <c r="O12" s="76" t="n"/>
-      <c r="P12" s="77" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="83" t="n"/>
+      <c r="O12" s="83" t="n"/>
+      <c r="P12" s="84" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="39" t="inlineStr">
@@ -1186,420 +1232,420 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="33">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8">
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="82" t="n"/>
+      <c r="F15" s="82" t="n"/>
+      <c r="G15" s="87" t="n"/>
+      <c r="H15" s="88" t="n"/>
+      <c r="I15" s="89">
         <f>IF(OR(G15="",H15=""),"",G15*H15)</f>
         <v/>
       </c>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="8">
+      <c r="J15" s="90" t="n"/>
+      <c r="K15" s="89">
         <f>IF(I15="","",I15*(1+N(J15)))</f>
         <v/>
       </c>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="23" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
+      <c r="O15" s="86" t="n"/>
+      <c r="P15" s="82" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="33">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8">
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="82" t="n"/>
+      <c r="F16" s="82" t="n"/>
+      <c r="G16" s="87" t="n"/>
+      <c r="H16" s="88" t="n"/>
+      <c r="I16" s="89">
         <f>IF(OR(G16="",H16=""),"",G16*H16)</f>
         <v/>
       </c>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="8">
+      <c r="J16" s="90" t="n"/>
+      <c r="K16" s="89">
         <f>IF(I16="","",I16*(1+N(J16)))</f>
         <v/>
       </c>
-      <c r="L16" s="23" t="n"/>
-      <c r="M16" s="23" t="n"/>
-      <c r="N16" s="23" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="23" t="n"/>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
+      <c r="N16" s="82" t="n"/>
+      <c r="O16" s="86" t="n"/>
+      <c r="P16" s="82" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="33">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8">
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="87" t="n"/>
+      <c r="H17" s="88" t="n"/>
+      <c r="I17" s="89">
         <f>IF(OR(G17="",H17=""),"",G17*H17)</f>
         <v/>
       </c>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="8">
+      <c r="J17" s="90" t="n"/>
+      <c r="K17" s="89">
         <f>IF(I17="","",I17*(1+N(J17)))</f>
         <v/>
       </c>
-      <c r="L17" s="23" t="n"/>
-      <c r="M17" s="23" t="n"/>
-      <c r="N17" s="23" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="23" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="86" t="n"/>
+      <c r="P17" s="82" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="33">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8">
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="87" t="n"/>
+      <c r="H18" s="88" t="n"/>
+      <c r="I18" s="89">
         <f>IF(OR(G18="",H18=""),"",G18*H18)</f>
         <v/>
       </c>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="8">
+      <c r="J18" s="90" t="n"/>
+      <c r="K18" s="89">
         <f>IF(I18="","",I18*(1+N(J18)))</f>
         <v/>
       </c>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="23" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="23" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="86" t="n"/>
+      <c r="P18" s="82" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="33">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="19" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8">
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="87" t="n"/>
+      <c r="H19" s="88" t="n"/>
+      <c r="I19" s="89">
         <f>IF(OR(G19="",H19=""),"",G19*H19)</f>
         <v/>
       </c>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="8">
+      <c r="J19" s="90" t="n"/>
+      <c r="K19" s="89">
         <f>IF(I19="","",I19*(1+N(J19)))</f>
         <v/>
       </c>
-      <c r="L19" s="23" t="n"/>
-      <c r="M19" s="23" t="n"/>
-      <c r="N19" s="23" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="23" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="86" t="n"/>
+      <c r="P19" s="82" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="33">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8">
+      <c r="B20" s="86" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="87" t="n"/>
+      <c r="H20" s="88" t="n"/>
+      <c r="I20" s="89">
         <f>IF(OR(G20="",H20=""),"",G20*H20)</f>
         <v/>
       </c>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="8">
+      <c r="J20" s="90" t="n"/>
+      <c r="K20" s="89">
         <f>IF(I20="","",I20*(1+N(J20)))</f>
         <v/>
       </c>
-      <c r="L20" s="23" t="n"/>
-      <c r="M20" s="23" t="n"/>
-      <c r="N20" s="23" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="23" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="86" t="n"/>
+      <c r="P20" s="82" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="33">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="85" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8">
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="82" t="n"/>
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="87" t="n"/>
+      <c r="H21" s="88" t="n"/>
+      <c r="I21" s="89">
         <f>IF(OR(G21="",H21=""),"",G21*H21)</f>
         <v/>
       </c>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="8">
+      <c r="J21" s="90" t="n"/>
+      <c r="K21" s="89">
         <f>IF(I21="","",I21*(1+N(J21)))</f>
         <v/>
       </c>
-      <c r="L21" s="23" t="n"/>
-      <c r="M21" s="23" t="n"/>
-      <c r="N21" s="23" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="23" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
+      <c r="O21" s="86" t="n"/>
+      <c r="P21" s="82" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="33">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8">
+      <c r="B22" s="86" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="87" t="n"/>
+      <c r="H22" s="88" t="n"/>
+      <c r="I22" s="89">
         <f>IF(OR(G22="",H22=""),"",G22*H22)</f>
         <v/>
       </c>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="8">
+      <c r="J22" s="90" t="n"/>
+      <c r="K22" s="89">
         <f>IF(I22="","",I22*(1+N(J22)))</f>
         <v/>
       </c>
-      <c r="L22" s="23" t="n"/>
-      <c r="M22" s="23" t="n"/>
-      <c r="N22" s="23" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="23" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="86" t="n"/>
+      <c r="P22" s="82" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="33">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8">
+      <c r="B23" s="86" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="87" t="n"/>
+      <c r="H23" s="88" t="n"/>
+      <c r="I23" s="89">
         <f>IF(OR(G23="",H23=""),"",G23*H23)</f>
         <v/>
       </c>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="8">
+      <c r="J23" s="90" t="n"/>
+      <c r="K23" s="89">
         <f>IF(I23="","",I23*(1+N(J23)))</f>
         <v/>
       </c>
-      <c r="L23" s="23" t="n"/>
-      <c r="M23" s="23" t="n"/>
-      <c r="N23" s="23" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="23" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="86" t="n"/>
+      <c r="P23" s="82" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="33">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="85" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8">
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="87" t="n"/>
+      <c r="H24" s="88" t="n"/>
+      <c r="I24" s="89">
         <f>IF(OR(G24="",H24=""),"",G24*H24)</f>
         <v/>
       </c>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="8">
+      <c r="J24" s="90" t="n"/>
+      <c r="K24" s="89">
         <f>IF(I24="","",I24*(1+N(J24)))</f>
         <v/>
       </c>
-      <c r="L24" s="23" t="n"/>
-      <c r="M24" s="23" t="n"/>
-      <c r="N24" s="23" t="n"/>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="23" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="86" t="n"/>
+      <c r="P24" s="82" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="33">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8">
+      <c r="B25" s="86" t="n"/>
+      <c r="C25" s="82" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="82" t="n"/>
+      <c r="F25" s="82" t="n"/>
+      <c r="G25" s="87" t="n"/>
+      <c r="H25" s="88" t="n"/>
+      <c r="I25" s="89">
         <f>IF(OR(G25="",H25=""),"",G25*H25)</f>
         <v/>
       </c>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="8">
+      <c r="J25" s="90" t="n"/>
+      <c r="K25" s="89">
         <f>IF(I25="","",I25*(1+N(J25)))</f>
         <v/>
       </c>
-      <c r="L25" s="23" t="n"/>
-      <c r="M25" s="23" t="n"/>
-      <c r="N25" s="23" t="n"/>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="23" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
+      <c r="O25" s="86" t="n"/>
+      <c r="P25" s="82" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="33">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="8">
+      <c r="B26" s="86" t="n"/>
+      <c r="C26" s="82" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="82" t="n"/>
+      <c r="F26" s="82" t="n"/>
+      <c r="G26" s="87" t="n"/>
+      <c r="H26" s="88" t="n"/>
+      <c r="I26" s="89">
         <f>IF(OR(G26="",H26=""),"",G26*H26)</f>
         <v/>
       </c>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="8">
+      <c r="J26" s="90" t="n"/>
+      <c r="K26" s="89">
         <f>IF(I26="","",I26*(1+N(J26)))</f>
         <v/>
       </c>
-      <c r="L26" s="23" t="n"/>
-      <c r="M26" s="23" t="n"/>
-      <c r="N26" s="23" t="n"/>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="23" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
+      <c r="O26" s="86" t="n"/>
+      <c r="P26" s="82" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="33">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="8">
+      <c r="B27" s="86" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="87" t="n"/>
+      <c r="H27" s="88" t="n"/>
+      <c r="I27" s="89">
         <f>IF(OR(G27="",H27=""),"",G27*H27)</f>
         <v/>
       </c>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="8">
+      <c r="J27" s="90" t="n"/>
+      <c r="K27" s="89">
         <f>IF(I27="","",I27*(1+N(J27)))</f>
         <v/>
       </c>
-      <c r="L27" s="23" t="n"/>
-      <c r="M27" s="23" t="n"/>
-      <c r="N27" s="23" t="n"/>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="23" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
+      <c r="N27" s="82" t="n"/>
+      <c r="O27" s="86" t="n"/>
+      <c r="P27" s="82" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="33">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="8">
+      <c r="B28" s="86" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="n"/>
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="87" t="n"/>
+      <c r="H28" s="88" t="n"/>
+      <c r="I28" s="89">
         <f>IF(OR(G28="",H28=""),"",G28*H28)</f>
         <v/>
       </c>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="8">
+      <c r="J28" s="90" t="n"/>
+      <c r="K28" s="89">
         <f>IF(I28="","",I28*(1+N(J28)))</f>
         <v/>
       </c>
-      <c r="L28" s="23" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="23" t="n"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="23" t="n"/>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
+      <c r="N28" s="82" t="n"/>
+      <c r="O28" s="86" t="n"/>
+      <c r="P28" s="82" t="n"/>
     </row>
     <row r="29" ht="22.05" customHeight="1" s="33">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="8">
+      <c r="B29" s="86" t="n"/>
+      <c r="C29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="82" t="n"/>
+      <c r="F29" s="82" t="n"/>
+      <c r="G29" s="87" t="n"/>
+      <c r="H29" s="88" t="n"/>
+      <c r="I29" s="89">
         <f>IF(OR(G29="",H29=""),"",G29*H29)</f>
         <v/>
       </c>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="8">
+      <c r="J29" s="90" t="n"/>
+      <c r="K29" s="89">
         <f>IF(I29="","",I29*(1+N(J29)))</f>
         <v/>
       </c>
-      <c r="L29" s="23" t="n"/>
-      <c r="M29" s="23" t="n"/>
-      <c r="N29" s="23" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="23" t="n"/>
+      <c r="L29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
+      <c r="N29" s="82" t="n"/>
+      <c r="O29" s="86" t="n"/>
+      <c r="P29" s="82" t="n"/>
     </row>
     <row r="30" ht="22.05" customHeight="1" s="33">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8">
+      <c r="B30" s="86" t="n"/>
+      <c r="C30" s="82" t="n"/>
+      <c r="D30" s="82" t="n"/>
+      <c r="E30" s="82" t="n"/>
+      <c r="F30" s="82" t="n"/>
+      <c r="G30" s="87" t="n"/>
+      <c r="H30" s="88" t="n"/>
+      <c r="I30" s="89">
         <f>IF(OR(G30="",H30=""),"",G30*H30)</f>
         <v/>
       </c>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="8">
+      <c r="J30" s="90" t="n"/>
+      <c r="K30" s="89">
         <f>IF(I30="","",I30*(1+N(J30)))</f>
         <v/>
       </c>
-      <c r="L30" s="23" t="n"/>
-      <c r="M30" s="23" t="n"/>
-      <c r="N30" s="23" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="23" t="n"/>
+      <c r="L30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
+      <c r="N30" s="82" t="n"/>
+      <c r="O30" s="86" t="n"/>
+      <c r="P30" s="82" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="33">
       <c r="A31" s="35" t="inlineStr">
@@ -1614,12 +1660,12 @@
       <c r="F31" s="76" t="n"/>
       <c r="G31" s="76" t="n"/>
       <c r="H31" s="77" t="n"/>
-      <c r="I31" s="14">
+      <c r="I31" s="91">
         <f>SUM(I15:I30)</f>
         <v/>
       </c>
       <c r="J31" s="34" t="n"/>
-      <c r="K31" s="14">
+      <c r="K31" s="91">
         <f>SUM(K15:K30)</f>
         <v/>
       </c>
@@ -1662,7 +1708,7 @@
       <c r="C34" s="76" t="n"/>
       <c r="D34" s="76" t="n"/>
       <c r="E34" s="77" t="n"/>
-      <c r="F34" s="43">
+      <c r="F34" s="92">
         <f>SUMIF(P15:P30,"Aprobado",K15:K30)</f>
         <v/>
       </c>
@@ -1679,7 +1725,7 @@
       <c r="C35" s="76" t="n"/>
       <c r="D35" s="76" t="n"/>
       <c r="E35" s="77" t="n"/>
-      <c r="F35" s="43">
+      <c r="F35" s="92">
         <f>SUMIF(P15:P30,"Pendiente",K15:K30)</f>
         <v/>
       </c>
@@ -1696,7 +1742,7 @@
       <c r="C36" s="76" t="n"/>
       <c r="D36" s="76" t="n"/>
       <c r="E36" s="77" t="n"/>
-      <c r="F36" s="43">
+      <c r="F36" s="92">
         <f>SUMIF(P15:P30,"Rechazado",K15:K30)</f>
         <v/>
       </c>
@@ -1713,9 +1759,9 @@
       <c r="C37" s="76" t="n"/>
       <c r="D37" s="76" t="n"/>
       <c r="E37" s="77" t="n"/>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="76" t="n"/>
-      <c r="H37" s="77" t="n"/>
+      <c r="F37" s="88" t="n"/>
+      <c r="G37" s="83" t="n"/>
+      <c r="H37" s="84" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="33">
       <c r="A38" s="21" t="inlineStr">
@@ -1727,7 +1773,7 @@
       <c r="C38" s="76" t="n"/>
       <c r="D38" s="76" t="n"/>
       <c r="E38" s="77" t="n"/>
-      <c r="F38" s="43">
+      <c r="F38" s="92">
         <f>IF(F37="","",F37+F34)</f>
         <v/>
       </c>
@@ -1744,7 +1790,7 @@
       <c r="C39" s="76" t="n"/>
       <c r="D39" s="76" t="n"/>
       <c r="E39" s="77" t="n"/>
-      <c r="F39" s="44">
+      <c r="F39" s="93">
         <f>IF(OR(F37="",F37=0),"",F34/F37)</f>
         <v/>
       </c>
@@ -1808,11 +1854,11 @@
       </c>
       <c r="B43" s="76" t="n"/>
       <c r="C43" s="77" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="76" t="n"/>
-      <c r="F43" s="76" t="n"/>
-      <c r="G43" s="76" t="n"/>
-      <c r="H43" s="77" t="n"/>
+      <c r="D43" s="82" t="n"/>
+      <c r="E43" s="83" t="n"/>
+      <c r="F43" s="83" t="n"/>
+      <c r="G43" s="83" t="n"/>
+      <c r="H43" s="84" t="n"/>
       <c r="I43" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1820,11 +1866,11 @@
       </c>
       <c r="J43" s="76" t="n"/>
       <c r="K43" s="77" t="n"/>
-      <c r="L43" s="23" t="n"/>
-      <c r="M43" s="76" t="n"/>
-      <c r="N43" s="76" t="n"/>
-      <c r="O43" s="76" t="n"/>
-      <c r="P43" s="77" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="83" t="n"/>
+      <c r="N43" s="83" t="n"/>
+      <c r="O43" s="83" t="n"/>
+      <c r="P43" s="84" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="33">
       <c r="A44" s="21" t="inlineStr">
@@ -1834,11 +1880,11 @@
       </c>
       <c r="B44" s="76" t="n"/>
       <c r="C44" s="77" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="76" t="n"/>
-      <c r="F44" s="76" t="n"/>
-      <c r="G44" s="76" t="n"/>
-      <c r="H44" s="77" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="83" t="n"/>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="83" t="n"/>
+      <c r="H44" s="84" t="n"/>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1846,11 +1892,11 @@
       </c>
       <c r="J44" s="76" t="n"/>
       <c r="K44" s="77" t="n"/>
-      <c r="L44" s="23" t="n"/>
-      <c r="M44" s="76" t="n"/>
-      <c r="N44" s="76" t="n"/>
-      <c r="O44" s="76" t="n"/>
-      <c r="P44" s="77" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="83" t="n"/>
+      <c r="N44" s="83" t="n"/>
+      <c r="O44" s="83" t="n"/>
+      <c r="P44" s="84" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="33">
       <c r="A45" s="21" t="inlineStr">
@@ -1860,11 +1906,11 @@
       </c>
       <c r="B45" s="76" t="n"/>
       <c r="C45" s="77" t="n"/>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="76" t="n"/>
-      <c r="F45" s="76" t="n"/>
-      <c r="G45" s="76" t="n"/>
-      <c r="H45" s="77" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="83" t="n"/>
+      <c r="F45" s="83" t="n"/>
+      <c r="G45" s="83" t="n"/>
+      <c r="H45" s="84" t="n"/>
       <c r="I45" s="21" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1872,13 +1918,14 @@
       </c>
       <c r="J45" s="76" t="n"/>
       <c r="K45" s="77" t="n"/>
-      <c r="L45" s="23" t="n"/>
-      <c r="M45" s="76" t="n"/>
-      <c r="N45" s="76" t="n"/>
-      <c r="O45" s="76" t="n"/>
-      <c r="P45" s="77" t="n"/>
+      <c r="L45" s="82" t="n"/>
+      <c r="M45" s="83" t="n"/>
+      <c r="N45" s="83" t="n"/>
+      <c r="O45" s="83" t="n"/>
+      <c r="P45" s="84" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="58">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
